--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46078</v>
+        <v>46099</v>
       </c>
       <c r="C1" s="1">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="D1" s="1">
-        <v>46092</v>
+        <v>46113</v>
       </c>
       <c r="E1" s="1">
-        <v>46099</v>
+        <v>46120</v>
       </c>
       <c r="F1" s="1">
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="G1" s="1">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H1" s="1">
-        <v>46120</v>
+        <v>46141</v>
       </c>
       <c r="I1" s="1">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="J1" s="1">
-        <v>46134</v>
+        <v>46155</v>
       </c>
       <c r="K1" s="1">
-        <v>46141</v>
+        <v>46162</v>
       </c>
       <c r="L1" s="1">
-        <v>46148</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>27.2</v>
+        <v>35.2</v>
       </c>
       <c r="C2">
-        <v>27.5</v>
+        <v>41.1</v>
       </c>
       <c r="D2">
-        <v>27.9</v>
+        <v>48.9</v>
       </c>
       <c r="E2">
-        <v>28.3</v>
+        <v>58.5</v>
       </c>
       <c r="F2">
-        <v>28.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G2">
-        <v>29.1</v>
+        <v>82</v>
       </c>
       <c r="H2">
-        <v>29.7</v>
+        <v>95.2</v>
       </c>
       <c r="I2">
-        <v>30.2</v>
+        <v>108.5</v>
       </c>
       <c r="J2">
-        <v>30.9</v>
+        <v>121.2</v>
       </c>
       <c r="K2">
-        <v>31.7</v>
+        <v>132.7</v>
       </c>
       <c r="L2">
-        <v>32.6</v>
+        <v>142.2</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>31.7</v>
+        <v>42.7</v>
       </c>
       <c r="C3">
-        <v>32.1</v>
+        <v>49.8</v>
       </c>
       <c r="D3">
-        <v>32.3</v>
+        <v>58.7</v>
       </c>
       <c r="E3">
-        <v>32.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F3">
-        <v>32.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G3">
-        <v>31.8</v>
+        <v>95.8</v>
       </c>
       <c r="H3">
-        <v>31.4</v>
+        <v>110.2</v>
       </c>
       <c r="I3">
-        <v>31.2</v>
+        <v>124.4</v>
       </c>
       <c r="J3">
-        <v>31.1</v>
+        <v>137.7</v>
       </c>
       <c r="K3">
-        <v>31.2</v>
+        <v>149.3</v>
       </c>
       <c r="L3">
-        <v>31.6</v>
+        <v>158.5</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>27.9</v>
+        <v>32.4</v>
       </c>
       <c r="C4">
-        <v>27.3</v>
+        <v>37.2</v>
       </c>
       <c r="D4">
-        <v>26.6</v>
+        <v>43.7</v>
       </c>
       <c r="E4">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F4">
-        <v>25.6</v>
+        <v>61.9</v>
       </c>
       <c r="G4">
-        <v>25.2</v>
+        <v>73</v>
       </c>
       <c r="H4">
-        <v>25.1</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I4">
-        <v>25.1</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J4">
-        <v>25.3</v>
+        <v>108.4</v>
       </c>
       <c r="K4">
-        <v>25.7</v>
+        <v>118.7</v>
       </c>
       <c r="L4">
-        <v>26.2</v>
+        <v>127.4</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>40.2</v>
+        <v>49.1</v>
       </c>
       <c r="C5">
-        <v>40.4</v>
+        <v>55.2</v>
       </c>
       <c r="D5">
-        <v>40.2</v>
+        <v>63.1</v>
       </c>
       <c r="E5">
-        <v>39.6</v>
+        <v>73</v>
       </c>
       <c r="F5">
-        <v>38.7</v>
+        <v>84.7</v>
       </c>
       <c r="G5">
-        <v>37.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="H5">
-        <v>36.4</v>
+        <v>112.6</v>
       </c>
       <c r="I5">
-        <v>35.4</v>
+        <v>127.4</v>
       </c>
       <c r="J5">
-        <v>34.9</v>
+        <v>141.9</v>
       </c>
       <c r="K5">
-        <v>35</v>
+        <v>155.1</v>
       </c>
       <c r="L5">
-        <v>35.7</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>24.8</v>
+        <v>33.9</v>
       </c>
       <c r="C6">
-        <v>25.4</v>
+        <v>40.5</v>
       </c>
       <c r="D6">
-        <v>26.2</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>27.2</v>
+        <v>59.5</v>
       </c>
       <c r="F6">
-        <v>28.4</v>
+        <v>71.5</v>
       </c>
       <c r="G6">
-        <v>29.8</v>
+        <v>84.8</v>
       </c>
       <c r="H6">
-        <v>31.4</v>
+        <v>98.8</v>
       </c>
       <c r="I6">
-        <v>33.2</v>
+        <v>112.7</v>
       </c>
       <c r="J6">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="K6">
-        <v>36.8</v>
+        <v>137.8</v>
       </c>
       <c r="L6">
-        <v>38.7</v>
+        <v>147.4</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>21.2</v>
+        <v>25.6</v>
       </c>
       <c r="C7">
-        <v>21.2</v>
+        <v>30.3</v>
       </c>
       <c r="D7">
-        <v>21.3</v>
+        <v>36.9</v>
       </c>
       <c r="E7">
-        <v>21.7</v>
+        <v>45.2</v>
       </c>
       <c r="F7">
-        <v>22.2</v>
+        <v>55.2</v>
       </c>
       <c r="G7">
-        <v>22.9</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="H7">
-        <v>23.7</v>
+        <v>79</v>
       </c>
       <c r="I7">
-        <v>24.5</v>
+        <v>91.7</v>
       </c>
       <c r="J7">
-        <v>25.4</v>
+        <v>104.3</v>
       </c>
       <c r="K7">
-        <v>26.4</v>
+        <v>116</v>
       </c>
       <c r="L7">
-        <v>27.3</v>
+        <v>126.3</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>18.4</v>
+        <v>21.6</v>
       </c>
       <c r="C8">
-        <v>18.2</v>
+        <v>25.2</v>
       </c>
       <c r="D8">
-        <v>18.3</v>
+        <v>30.2</v>
       </c>
       <c r="E8">
-        <v>18.8</v>
+        <v>36.5</v>
       </c>
       <c r="F8">
-        <v>19.6</v>
+        <v>43.8</v>
       </c>
       <c r="G8">
-        <v>20.5</v>
+        <v>52.1</v>
       </c>
       <c r="H8">
-        <v>21.6</v>
+        <v>60.8</v>
       </c>
       <c r="I8">
-        <v>22.8</v>
+        <v>69.8</v>
       </c>
       <c r="J8">
-        <v>23.9</v>
+        <v>78.5</v>
       </c>
       <c r="K8">
-        <v>24.9</v>
+        <v>86.5</v>
       </c>
       <c r="L8">
-        <v>25.9</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>18.2</v>
+        <v>24.7</v>
       </c>
       <c r="C9">
-        <v>19.4</v>
+        <v>28.9</v>
       </c>
       <c r="D9">
-        <v>20.8</v>
+        <v>34.3</v>
       </c>
       <c r="E9">
-        <v>22.4</v>
+        <v>40.6</v>
       </c>
       <c r="F9">
-        <v>24</v>
+        <v>47.8</v>
       </c>
       <c r="G9">
-        <v>25.6</v>
+        <v>55.7</v>
       </c>
       <c r="H9">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="I9">
-        <v>28.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J9">
-        <v>29.1</v>
+        <v>80.5</v>
       </c>
       <c r="K9">
-        <v>29.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="L9">
-        <v>30.2</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>33.8</v>
+        <v>44.8</v>
       </c>
       <c r="C10">
-        <v>35.1</v>
+        <v>51.8</v>
       </c>
       <c r="D10">
-        <v>36.3</v>
+        <v>60.8</v>
       </c>
       <c r="E10">
-        <v>37.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F10">
-        <v>38.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="G10">
-        <v>39.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H10">
-        <v>40.7</v>
+        <v>112.5</v>
       </c>
       <c r="I10">
-        <v>41.7</v>
+        <v>127.2</v>
       </c>
       <c r="J10">
-        <v>42.7</v>
+        <v>141.2</v>
       </c>
       <c r="K10">
-        <v>43.7</v>
+        <v>153.7</v>
       </c>
       <c r="L10">
-        <v>44.7</v>
+        <v>163.9</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>18.4</v>
+        <v>31.5</v>
       </c>
       <c r="C11">
-        <v>19.2</v>
+        <v>40.8</v>
       </c>
       <c r="D11">
-        <v>20.4</v>
+        <v>52.6</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>66.8</v>
       </c>
       <c r="F11">
-        <v>23.9</v>
+        <v>83.2</v>
       </c>
       <c r="G11">
-        <v>26</v>
+        <v>101</v>
       </c>
       <c r="H11">
-        <v>28.4</v>
+        <v>119.6</v>
       </c>
       <c r="I11">
-        <v>30.9</v>
+        <v>137.9</v>
       </c>
       <c r="J11">
-        <v>33.4</v>
+        <v>155.2</v>
       </c>
       <c r="K11">
-        <v>35.9</v>
+        <v>170.3</v>
       </c>
       <c r="L11">
-        <v>38.2</v>
+        <v>182.5</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>37.5</v>
+        <v>45.5</v>
       </c>
       <c r="C12">
-        <v>37.1</v>
+        <v>51.6</v>
       </c>
       <c r="D12">
-        <v>36.3</v>
+        <v>59.7</v>
       </c>
       <c r="E12">
-        <v>35.3</v>
+        <v>69.8</v>
       </c>
       <c r="F12">
-        <v>33.9</v>
+        <v>81.8</v>
       </c>
       <c r="G12">
-        <v>32.4</v>
+        <v>95.3</v>
       </c>
       <c r="H12">
-        <v>30.9</v>
+        <v>109.8</v>
       </c>
       <c r="I12">
-        <v>29.4</v>
+        <v>124.5</v>
       </c>
       <c r="J12">
-        <v>28.2</v>
+        <v>138.7</v>
       </c>
       <c r="K12">
-        <v>27.4</v>
+        <v>151.5</v>
       </c>
       <c r="L12">
-        <v>27.1</v>
+        <v>162.1</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46099</v>
+        <v>46134</v>
       </c>
       <c r="C1" s="1">
-        <v>46106</v>
+        <v>46141</v>
       </c>
       <c r="D1" s="1">
-        <v>46113</v>
+        <v>46148</v>
       </c>
       <c r="E1" s="1">
-        <v>46120</v>
+        <v>46155</v>
       </c>
       <c r="F1" s="1">
-        <v>46127</v>
+        <v>46162</v>
       </c>
       <c r="G1" s="1">
-        <v>46134</v>
+        <v>46169</v>
       </c>
       <c r="H1" s="1">
-        <v>46141</v>
+        <v>46176</v>
       </c>
       <c r="I1" s="1">
-        <v>46148</v>
+        <v>46183</v>
       </c>
       <c r="J1" s="1">
-        <v>46155</v>
+        <v>46190</v>
       </c>
       <c r="K1" s="1">
-        <v>46162</v>
+        <v>46197</v>
       </c>
       <c r="L1" s="1">
-        <v>46169</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>35.2</v>
+        <v>69.2</v>
       </c>
       <c r="C2">
-        <v>41.1</v>
+        <v>75.3</v>
       </c>
       <c r="D2">
-        <v>48.9</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E2">
-        <v>58.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F2">
-        <v>69.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G2">
-        <v>82</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H2">
-        <v>95.2</v>
+        <v>77</v>
       </c>
       <c r="I2">
-        <v>108.5</v>
+        <v>70.3</v>
       </c>
       <c r="J2">
-        <v>121.2</v>
+        <v>61.9</v>
       </c>
       <c r="K2">
-        <v>132.7</v>
+        <v>52.2</v>
       </c>
       <c r="L2">
-        <v>142.2</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>42.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="C3">
-        <v>49.8</v>
+        <v>78.5</v>
       </c>
       <c r="D3">
-        <v>58.7</v>
+        <v>81.8</v>
       </c>
       <c r="E3">
-        <v>69.59999999999999</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="F3">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="G3">
-        <v>95.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H3">
-        <v>110.2</v>
+        <v>73.7</v>
       </c>
       <c r="I3">
-        <v>124.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J3">
-        <v>137.7</v>
+        <v>57.8</v>
       </c>
       <c r="K3">
-        <v>149.3</v>
+        <v>48.3</v>
       </c>
       <c r="L3">
-        <v>158.5</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>32.4</v>
+        <v>62.1</v>
       </c>
       <c r="C4">
-        <v>37.2</v>
+        <v>68.8</v>
       </c>
       <c r="D4">
-        <v>43.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E4">
-        <v>52</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F4">
-        <v>61.9</v>
+        <v>82</v>
       </c>
       <c r="G4">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H4">
-        <v>84.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I4">
-        <v>96.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="J4">
-        <v>108.4</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K4">
-        <v>118.7</v>
+        <v>69.2</v>
       </c>
       <c r="L4">
-        <v>127.4</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>49.1</v>
+        <v>80</v>
       </c>
       <c r="C5">
-        <v>55.2</v>
+        <v>85.5</v>
       </c>
       <c r="D5">
-        <v>63.1</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="E5">
-        <v>73</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="F5">
-        <v>84.7</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G5">
-        <v>98.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="H5">
-        <v>112.6</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I5">
-        <v>127.4</v>
+        <v>76.5</v>
       </c>
       <c r="J5">
-        <v>141.9</v>
+        <v>67</v>
       </c>
       <c r="K5">
-        <v>155.1</v>
+        <v>56.2</v>
       </c>
       <c r="L5">
-        <v>166</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>33.9</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="C6">
-        <v>40.5</v>
+        <v>72.8</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>74.7</v>
       </c>
       <c r="E6">
-        <v>59.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F6">
-        <v>71.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G6">
-        <v>84.8</v>
+        <v>61.9</v>
       </c>
       <c r="H6">
-        <v>98.8</v>
+        <v>51.6</v>
       </c>
       <c r="I6">
-        <v>112.7</v>
+        <v>38.9</v>
       </c>
       <c r="J6">
-        <v>126</v>
+        <v>24.6</v>
       </c>
       <c r="K6">
-        <v>137.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L6">
-        <v>147.4</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>25.6</v>
+        <v>60.2</v>
       </c>
       <c r="C7">
-        <v>30.3</v>
+        <v>67.8</v>
       </c>
       <c r="D7">
-        <v>36.9</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E7">
-        <v>45.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F7">
-        <v>55.2</v>
+        <v>83.3</v>
       </c>
       <c r="G7">
-        <v>66.59999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H7">
-        <v>79</v>
+        <v>83.5</v>
       </c>
       <c r="I7">
-        <v>91.7</v>
+        <v>80.2</v>
       </c>
       <c r="J7">
-        <v>104.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K7">
-        <v>116</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L7">
-        <v>126.3</v>
+        <v>59.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>21.6</v>
+        <v>49.5</v>
       </c>
       <c r="C8">
-        <v>25.2</v>
+        <v>56.4</v>
       </c>
       <c r="D8">
-        <v>30.2</v>
+        <v>62.8</v>
       </c>
       <c r="E8">
-        <v>36.5</v>
+        <v>68.5</v>
       </c>
       <c r="F8">
-        <v>43.8</v>
+        <v>73</v>
       </c>
       <c r="G8">
-        <v>52.1</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="H8">
-        <v>60.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I8">
-        <v>69.8</v>
+        <v>77.5</v>
       </c>
       <c r="J8">
-        <v>78.5</v>
+        <v>75.8</v>
       </c>
       <c r="K8">
-        <v>86.5</v>
+        <v>72.7</v>
       </c>
       <c r="L8">
-        <v>93.5</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>24.7</v>
+        <v>57.6</v>
       </c>
       <c r="C9">
-        <v>28.9</v>
+        <v>64.7</v>
       </c>
       <c r="D9">
-        <v>34.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E9">
-        <v>40.6</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F9">
-        <v>47.8</v>
+        <v>79.3</v>
       </c>
       <c r="G9">
-        <v>55.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H9">
-        <v>64</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I9">
-        <v>72.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="J9">
-        <v>80.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K9">
-        <v>87.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="L9">
-        <v>94.5</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>44.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="C10">
-        <v>51.8</v>
+        <v>87.7</v>
       </c>
       <c r="D10">
-        <v>60.8</v>
+        <v>90.5</v>
       </c>
       <c r="E10">
-        <v>71.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="F10">
-        <v>84.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G10">
-        <v>97.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H10">
-        <v>112.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I10">
-        <v>127.2</v>
+        <v>57.1</v>
       </c>
       <c r="J10">
-        <v>141.2</v>
+        <v>42.2</v>
       </c>
       <c r="K10">
-        <v>153.7</v>
+        <v>26.4</v>
       </c>
       <c r="L10">
-        <v>163.9</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>31.5</v>
+        <v>83.3</v>
       </c>
       <c r="C11">
-        <v>40.8</v>
+        <v>91.8</v>
       </c>
       <c r="D11">
-        <v>52.6</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E11">
-        <v>66.8</v>
+        <v>100.7</v>
       </c>
       <c r="F11">
-        <v>83.2</v>
+        <v>99.8</v>
       </c>
       <c r="G11">
-        <v>101</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H11">
-        <v>119.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I11">
-        <v>137.9</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J11">
-        <v>155.2</v>
+        <v>60.8</v>
       </c>
       <c r="K11">
-        <v>170.3</v>
+        <v>45.3</v>
       </c>
       <c r="L11">
-        <v>182.5</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>45.5</v>
+        <v>74.2</v>
       </c>
       <c r="C12">
-        <v>51.6</v>
+        <v>79.3</v>
       </c>
       <c r="D12">
-        <v>59.7</v>
+        <v>83.3</v>
       </c>
       <c r="E12">
-        <v>69.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F12">
-        <v>81.8</v>
+        <v>86</v>
       </c>
       <c r="G12">
-        <v>95.3</v>
+        <v>84.2</v>
       </c>
       <c r="H12">
-        <v>109.8</v>
+        <v>80.3</v>
       </c>
       <c r="I12">
-        <v>124.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="J12">
-        <v>138.7</v>
+        <v>67</v>
       </c>
       <c r="K12">
-        <v>151.5</v>
+        <v>58.5</v>
       </c>
       <c r="L12">
-        <v>162.1</v>
+        <v>49.7</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46134</v>
+        <v>46162</v>
       </c>
       <c r="C1" s="1">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="D1" s="1">
-        <v>46148</v>
+        <v>46176</v>
       </c>
       <c r="E1" s="1">
-        <v>46155</v>
+        <v>46183</v>
       </c>
       <c r="F1" s="1">
-        <v>46162</v>
+        <v>46190</v>
       </c>
       <c r="G1" s="1">
-        <v>46169</v>
+        <v>46197</v>
       </c>
       <c r="H1" s="1">
-        <v>46176</v>
+        <v>46204</v>
       </c>
       <c r="I1" s="1">
-        <v>46183</v>
+        <v>46211</v>
       </c>
       <c r="J1" s="1">
-        <v>46190</v>
+        <v>46218</v>
       </c>
       <c r="K1" s="1">
-        <v>46197</v>
+        <v>46225</v>
       </c>
       <c r="L1" s="1">
-        <v>46204</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>69.2</v>
+        <v>87.7</v>
       </c>
       <c r="C2">
-        <v>75.3</v>
+        <v>88.7</v>
       </c>
       <c r="D2">
-        <v>80.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="E2">
-        <v>82.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="F2">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="G2">
-        <v>81.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="H2">
-        <v>77</v>
+        <v>75.5</v>
       </c>
       <c r="I2">
-        <v>70.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="J2">
-        <v>61.9</v>
+        <v>68.3</v>
       </c>
       <c r="K2">
-        <v>52.2</v>
+        <v>65.8</v>
       </c>
       <c r="L2">
-        <v>42.1</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>73.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="C3">
-        <v>78.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D3">
-        <v>81.8</v>
+        <v>85.5</v>
       </c>
       <c r="E3">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F3">
-        <v>82.3</v>
+        <v>79.3</v>
       </c>
       <c r="G3">
-        <v>79.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H3">
-        <v>73.7</v>
+        <v>71.5</v>
       </c>
       <c r="I3">
-        <v>66.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="J3">
-        <v>57.8</v>
+        <v>65.2</v>
       </c>
       <c r="K3">
-        <v>48.3</v>
+        <v>63.2</v>
       </c>
       <c r="L3">
-        <v>38.9</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>62.1</v>
+        <v>83.2</v>
       </c>
       <c r="C4">
-        <v>68.8</v>
+        <v>85.2</v>
       </c>
       <c r="D4">
-        <v>74.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="E4">
-        <v>79.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="F4">
-        <v>82</v>
+        <v>81.7</v>
       </c>
       <c r="G4">
-        <v>83</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H4">
-        <v>82.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="I4">
-        <v>79.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J4">
-        <v>74.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K4">
-        <v>69.2</v>
+        <v>60.4</v>
       </c>
       <c r="L4">
-        <v>62.7</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>80</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C5">
-        <v>85.5</v>
+        <v>98.7</v>
       </c>
       <c r="D5">
-        <v>89.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="E5">
-        <v>91.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F5">
-        <v>91.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="G5">
-        <v>89.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H5">
-        <v>84.09999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I5">
-        <v>76.5</v>
+        <v>86</v>
       </c>
       <c r="J5">
-        <v>67</v>
+        <v>83.7</v>
       </c>
       <c r="K5">
-        <v>56.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L5">
-        <v>44.8</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>68.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C6">
-        <v>72.8</v>
+        <v>79.2</v>
       </c>
       <c r="D6">
-        <v>74.7</v>
+        <v>77</v>
       </c>
       <c r="E6">
-        <v>73.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F6">
-        <v>69.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G6">
-        <v>61.9</v>
+        <v>67</v>
       </c>
       <c r="H6">
-        <v>51.6</v>
+        <v>64.2</v>
       </c>
       <c r="I6">
-        <v>38.9</v>
+        <v>62.3</v>
       </c>
       <c r="J6">
-        <v>24.6</v>
+        <v>61.7</v>
       </c>
       <c r="K6">
-        <v>9.699999999999999</v>
+        <v>62.3</v>
       </c>
       <c r="L6">
-        <v>-4.7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>60.2</v>
+        <v>85</v>
       </c>
       <c r="C7">
-        <v>67.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D7">
-        <v>74.59999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="E7">
-        <v>79.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="F7">
-        <v>83.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G7">
-        <v>84.59999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H7">
-        <v>83.5</v>
+        <v>75.7</v>
       </c>
       <c r="I7">
-        <v>80.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="J7">
-        <v>74.90000000000001</v>
+        <v>65.2</v>
       </c>
       <c r="K7">
-        <v>67.90000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="L7">
-        <v>59.9</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>49.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="C8">
-        <v>56.4</v>
+        <v>71.7</v>
       </c>
       <c r="D8">
-        <v>62.8</v>
+        <v>71.8</v>
       </c>
       <c r="E8">
-        <v>68.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F8">
-        <v>73</v>
+        <v>66.8</v>
       </c>
       <c r="G8">
-        <v>76.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="H8">
-        <v>77.59999999999999</v>
+        <v>56.6</v>
       </c>
       <c r="I8">
-        <v>77.5</v>
+        <v>50.5</v>
       </c>
       <c r="J8">
-        <v>75.8</v>
+        <v>44.3</v>
       </c>
       <c r="K8">
-        <v>72.7</v>
+        <v>38.6</v>
       </c>
       <c r="L8">
-        <v>68.5</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>57.6</v>
+        <v>78.7</v>
       </c>
       <c r="C9">
-        <v>64.7</v>
+        <v>80.3</v>
       </c>
       <c r="D9">
-        <v>70.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="E9">
-        <v>75.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="F9">
-        <v>79.3</v>
+        <v>74.8</v>
       </c>
       <c r="G9">
-        <v>80.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H9">
-        <v>80.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="I9">
-        <v>77.90000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="J9">
-        <v>73.59999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="K9">
-        <v>67.8</v>
+        <v>47.2</v>
       </c>
       <c r="L9">
-        <v>60.9</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>82.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="C10">
-        <v>87.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D10">
-        <v>90.5</v>
+        <v>95</v>
       </c>
       <c r="E10">
-        <v>90.3</v>
+        <v>92.3</v>
       </c>
       <c r="F10">
-        <v>86.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="G10">
-        <v>80</v>
+        <v>85.7</v>
       </c>
       <c r="H10">
-        <v>69.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="I10">
-        <v>57.1</v>
+        <v>80.7</v>
       </c>
       <c r="J10">
-        <v>42.2</v>
+        <v>79.7</v>
       </c>
       <c r="K10">
-        <v>26.4</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="L10">
-        <v>10.6</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>83.3</v>
+        <v>108.5</v>
       </c>
       <c r="C11">
-        <v>91.8</v>
+        <v>109.8</v>
       </c>
       <c r="D11">
-        <v>97.90000000000001</v>
+        <v>109.1</v>
       </c>
       <c r="E11">
-        <v>100.7</v>
+        <v>106.9</v>
       </c>
       <c r="F11">
-        <v>99.8</v>
+        <v>103.5</v>
       </c>
       <c r="G11">
-        <v>95.09999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="H11">
-        <v>86.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="I11">
-        <v>74.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J11">
-        <v>60.8</v>
+        <v>90.8</v>
       </c>
       <c r="K11">
-        <v>45.3</v>
+        <v>89.8</v>
       </c>
       <c r="L11">
-        <v>29.4</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>74.2</v>
+        <v>90</v>
       </c>
       <c r="C12">
-        <v>79.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D12">
-        <v>83.3</v>
+        <v>90.8</v>
       </c>
       <c r="E12">
-        <v>85.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="F12">
-        <v>86</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="G12">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="H12">
-        <v>80.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I12">
-        <v>74.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="J12">
-        <v>67</v>
+        <v>75.5</v>
       </c>
       <c r="K12">
-        <v>58.5</v>
+        <v>73.8</v>
       </c>
       <c r="L12">
-        <v>49.7</v>
+        <v>72.7</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46162</v>
+        <v>46197</v>
       </c>
       <c r="C1" s="1">
-        <v>46169</v>
+        <v>46204</v>
       </c>
       <c r="D1" s="1">
-        <v>46176</v>
+        <v>46211</v>
       </c>
       <c r="E1" s="1">
-        <v>46183</v>
+        <v>46218</v>
       </c>
       <c r="F1" s="1">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="G1" s="1">
-        <v>46197</v>
+        <v>46232</v>
       </c>
       <c r="H1" s="1">
-        <v>46204</v>
+        <v>46239</v>
       </c>
       <c r="I1" s="1">
-        <v>46211</v>
+        <v>46246</v>
       </c>
       <c r="J1" s="1">
-        <v>46218</v>
+        <v>46253</v>
       </c>
       <c r="K1" s="1">
-        <v>46225</v>
+        <v>46260</v>
       </c>
       <c r="L1" s="1">
-        <v>46232</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>87.7</v>
+        <v>80</v>
       </c>
       <c r="C2">
-        <v>88.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D2">
-        <v>88.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E2">
-        <v>86.3</v>
+        <v>68.2</v>
       </c>
       <c r="F2">
-        <v>83.2</v>
+        <v>65.2</v>
       </c>
       <c r="G2">
-        <v>79.5</v>
+        <v>62.8</v>
       </c>
       <c r="H2">
-        <v>75.5</v>
+        <v>61.1</v>
       </c>
       <c r="I2">
-        <v>71.59999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="J2">
-        <v>68.3</v>
+        <v>59</v>
       </c>
       <c r="K2">
-        <v>65.8</v>
+        <v>58.2</v>
       </c>
       <c r="L2">
-        <v>64.09999999999999</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>87.2</v>
+        <v>73.2</v>
       </c>
       <c r="C3">
-        <v>87.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="D3">
-        <v>85.5</v>
+        <v>62.6</v>
       </c>
       <c r="E3">
-        <v>82.90000000000001</v>
+        <v>57.6</v>
       </c>
       <c r="F3">
-        <v>79.3</v>
+        <v>53.1</v>
       </c>
       <c r="G3">
-        <v>75.40000000000001</v>
+        <v>49.3</v>
       </c>
       <c r="H3">
-        <v>71.5</v>
+        <v>46</v>
       </c>
       <c r="I3">
-        <v>68</v>
+        <v>43.3</v>
       </c>
       <c r="J3">
-        <v>65.2</v>
+        <v>40.9</v>
       </c>
       <c r="K3">
-        <v>63.2</v>
+        <v>38.9</v>
       </c>
       <c r="L3">
-        <v>62.1</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>83.2</v>
+        <v>81.8</v>
       </c>
       <c r="C4">
-        <v>85.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D4">
-        <v>85.5</v>
+        <v>76.3</v>
       </c>
       <c r="E4">
-        <v>84.3</v>
+        <v>73.7</v>
       </c>
       <c r="F4">
-        <v>81.7</v>
+        <v>71.5</v>
       </c>
       <c r="G4">
-        <v>78.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H4">
-        <v>73.7</v>
+        <v>68.8</v>
       </c>
       <c r="I4">
-        <v>69.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="J4">
-        <v>64.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K4">
-        <v>60.4</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="L4">
-        <v>57</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>97.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="C5">
-        <v>98.7</v>
+        <v>83.3</v>
       </c>
       <c r="D5">
-        <v>98.7</v>
+        <v>77</v>
       </c>
       <c r="E5">
-        <v>97.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F5">
-        <v>95</v>
+        <v>63.9</v>
       </c>
       <c r="G5">
-        <v>92.09999999999999</v>
+        <v>57.6</v>
       </c>
       <c r="H5">
-        <v>88.90000000000001</v>
+        <v>51.7</v>
       </c>
       <c r="I5">
-        <v>86</v>
+        <v>46.1</v>
       </c>
       <c r="J5">
-        <v>83.7</v>
+        <v>41</v>
       </c>
       <c r="K5">
-        <v>82.09999999999999</v>
+        <v>36.3</v>
       </c>
       <c r="L5">
-        <v>81.3</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>80.09999999999999</v>
+        <v>62.9</v>
       </c>
       <c r="C6">
-        <v>79.2</v>
+        <v>57.2</v>
       </c>
       <c r="D6">
-        <v>77</v>
+        <v>51.8</v>
       </c>
       <c r="E6">
-        <v>73.90000000000001</v>
+        <v>46.8</v>
       </c>
       <c r="F6">
-        <v>70.40000000000001</v>
+        <v>42.5</v>
       </c>
       <c r="G6">
-        <v>67</v>
+        <v>38.8</v>
       </c>
       <c r="H6">
-        <v>64.2</v>
+        <v>35.7</v>
       </c>
       <c r="I6">
-        <v>62.3</v>
+        <v>33.1</v>
       </c>
       <c r="J6">
-        <v>61.7</v>
+        <v>30.8</v>
       </c>
       <c r="K6">
-        <v>62.3</v>
+        <v>28.7</v>
       </c>
       <c r="L6">
-        <v>64</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="C7">
+        <v>85.7</v>
+      </c>
+      <c r="D7">
         <v>85</v>
       </c>
-      <c r="C7">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="D7">
-        <v>88.3</v>
-      </c>
       <c r="E7">
-        <v>87.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F7">
-        <v>84.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="G7">
-        <v>80.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="H7">
-        <v>75.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I7">
-        <v>70.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J7">
-        <v>65.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="K7">
-        <v>60.4</v>
+        <v>100.5</v>
       </c>
       <c r="L7">
-        <v>56.4</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="C8">
-        <v>71.7</v>
+        <v>63.5</v>
       </c>
       <c r="D8">
-        <v>71.8</v>
+        <v>61.4</v>
       </c>
       <c r="E8">
-        <v>70.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="F8">
-        <v>66.8</v>
+        <v>59.7</v>
       </c>
       <c r="G8">
-        <v>62.1</v>
+        <v>60.6</v>
       </c>
       <c r="H8">
-        <v>56.6</v>
+        <v>62.6</v>
       </c>
       <c r="I8">
-        <v>50.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J8">
-        <v>44.3</v>
+        <v>69.3</v>
       </c>
       <c r="K8">
-        <v>38.6</v>
+        <v>73.3</v>
       </c>
       <c r="L8">
-        <v>33.7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>78.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C9">
-        <v>80.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D9">
-        <v>80.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E9">
-        <v>78.3</v>
+        <v>68</v>
       </c>
       <c r="F9">
-        <v>74.8</v>
+        <v>67</v>
       </c>
       <c r="G9">
-        <v>70.09999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H9">
-        <v>64.5</v>
+        <v>68.2</v>
       </c>
       <c r="I9">
-        <v>58.5</v>
+        <v>70.2</v>
       </c>
       <c r="J9">
-        <v>52.6</v>
+        <v>72.7</v>
       </c>
       <c r="K9">
-        <v>47.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L9">
-        <v>42.7</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>96.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="C10">
-        <v>96.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D10">
-        <v>95</v>
+        <v>71.2</v>
       </c>
       <c r="E10">
-        <v>92.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F10">
-        <v>89.09999999999999</v>
+        <v>61.1</v>
       </c>
       <c r="G10">
-        <v>85.7</v>
+        <v>56.8</v>
       </c>
       <c r="H10">
-        <v>82.8</v>
+        <v>53</v>
       </c>
       <c r="I10">
-        <v>80.7</v>
+        <v>49.5</v>
       </c>
       <c r="J10">
-        <v>79.7</v>
+        <v>46.2</v>
       </c>
       <c r="K10">
-        <v>79.90000000000001</v>
+        <v>42.9</v>
       </c>
       <c r="L10">
-        <v>81.09999999999999</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>108.5</v>
+        <v>99.5</v>
       </c>
       <c r="C11">
-        <v>109.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D11">
-        <v>109.1</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E11">
-        <v>106.9</v>
+        <v>86.3</v>
       </c>
       <c r="F11">
-        <v>103.5</v>
+        <v>83</v>
       </c>
       <c r="G11">
-        <v>99.7</v>
+        <v>80.3</v>
       </c>
       <c r="H11">
-        <v>96</v>
+        <v>78.2</v>
       </c>
       <c r="I11">
-        <v>92.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="J11">
-        <v>90.8</v>
+        <v>74.5</v>
       </c>
       <c r="K11">
-        <v>89.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="L11">
-        <v>89.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>90</v>
+        <v>82.8</v>
       </c>
       <c r="C12">
-        <v>91.09999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="D12">
-        <v>90.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E12">
-        <v>89.3</v>
+        <v>68.8</v>
       </c>
       <c r="F12">
-        <v>86.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="G12">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="H12">
-        <v>80.90000000000001</v>
+        <v>56.1</v>
       </c>
       <c r="I12">
-        <v>78</v>
+        <v>52.5</v>
       </c>
       <c r="J12">
-        <v>75.5</v>
+        <v>49.2</v>
       </c>
       <c r="K12">
-        <v>73.8</v>
+        <v>46.1</v>
       </c>
       <c r="L12">
-        <v>72.7</v>
+        <v>43.2</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46197</v>
+        <v>46260</v>
       </c>
       <c r="C1" s="1">
-        <v>46204</v>
+        <v>46267</v>
       </c>
       <c r="D1" s="1">
-        <v>46211</v>
+        <v>46274</v>
       </c>
       <c r="E1" s="1">
-        <v>46218</v>
+        <v>46281</v>
       </c>
       <c r="F1" s="1">
-        <v>46225</v>
+        <v>46288</v>
       </c>
       <c r="G1" s="1">
-        <v>46232</v>
+        <v>46295</v>
       </c>
       <c r="H1" s="1">
-        <v>46239</v>
+        <v>46302</v>
       </c>
       <c r="I1" s="1">
-        <v>46246</v>
+        <v>46309</v>
       </c>
       <c r="J1" s="1">
-        <v>46253</v>
+        <v>46316</v>
       </c>
       <c r="K1" s="1">
-        <v>46260</v>
+        <v>46323</v>
       </c>
       <c r="L1" s="1">
-        <v>46267</v>
+        <v>46330</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>80</v>
+        <v>54.6</v>
       </c>
       <c r="C2">
-        <v>75.90000000000001</v>
+        <v>53.9</v>
       </c>
       <c r="D2">
-        <v>71.90000000000001</v>
+        <v>53.3</v>
       </c>
       <c r="E2">
-        <v>68.2</v>
+        <v>52.6</v>
       </c>
       <c r="F2">
-        <v>65.2</v>
+        <v>52</v>
       </c>
       <c r="G2">
-        <v>62.8</v>
+        <v>51.4</v>
       </c>
       <c r="H2">
-        <v>61.1</v>
+        <v>50.8</v>
       </c>
       <c r="I2">
-        <v>59.9</v>
+        <v>50.3</v>
       </c>
       <c r="J2">
-        <v>59</v>
+        <v>49.8</v>
       </c>
       <c r="K2">
-        <v>58.2</v>
+        <v>49.4</v>
       </c>
       <c r="L2">
-        <v>57.3</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>73.2</v>
+        <v>49.2</v>
       </c>
       <c r="C3">
-        <v>67.90000000000001</v>
+        <v>48.9</v>
       </c>
       <c r="D3">
-        <v>62.6</v>
+        <v>48.6</v>
       </c>
       <c r="E3">
-        <v>57.6</v>
+        <v>48.2</v>
       </c>
       <c r="F3">
-        <v>53.1</v>
+        <v>47.7</v>
       </c>
       <c r="G3">
-        <v>49.3</v>
+        <v>47</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="I3">
-        <v>43.3</v>
+        <v>45.5</v>
       </c>
       <c r="J3">
-        <v>40.9</v>
+        <v>44.7</v>
       </c>
       <c r="K3">
-        <v>38.9</v>
+        <v>43.8</v>
       </c>
       <c r="L3">
-        <v>37.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>81.8</v>
+        <v>58.3</v>
       </c>
       <c r="C4">
-        <v>79.09999999999999</v>
+        <v>56.5</v>
       </c>
       <c r="D4">
-        <v>76.3</v>
+        <v>54.8</v>
       </c>
       <c r="E4">
-        <v>73.7</v>
+        <v>53.2</v>
       </c>
       <c r="F4">
-        <v>71.5</v>
+        <v>51.6</v>
       </c>
       <c r="G4">
-        <v>69.90000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="H4">
-        <v>68.8</v>
+        <v>49</v>
       </c>
       <c r="I4">
-        <v>68</v>
+        <v>48.1</v>
       </c>
       <c r="J4">
-        <v>67.59999999999999</v>
+        <v>47.4</v>
       </c>
       <c r="K4">
-        <v>67.09999999999999</v>
+        <v>47</v>
       </c>
       <c r="L4">
-        <v>66.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>89</v>
+        <v>45.5</v>
       </c>
       <c r="C5">
-        <v>83.3</v>
+        <v>42.9</v>
       </c>
       <c r="D5">
-        <v>77</v>
+        <v>40.6</v>
       </c>
       <c r="E5">
-        <v>70.40000000000001</v>
+        <v>38.6</v>
       </c>
       <c r="F5">
-        <v>63.9</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>57.6</v>
+        <v>35.8</v>
       </c>
       <c r="H5">
-        <v>51.7</v>
+        <v>34.9</v>
       </c>
       <c r="I5">
-        <v>46.1</v>
+        <v>34.3</v>
       </c>
       <c r="J5">
-        <v>41</v>
+        <v>34.1</v>
       </c>
       <c r="K5">
-        <v>36.3</v>
+        <v>34.2</v>
       </c>
       <c r="L5">
-        <v>32.1</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>62.9</v>
+        <v>41.4</v>
       </c>
       <c r="C6">
-        <v>57.2</v>
+        <v>41.5</v>
       </c>
       <c r="D6">
-        <v>51.8</v>
+        <v>41.6</v>
       </c>
       <c r="E6">
-        <v>46.8</v>
+        <v>41.5</v>
       </c>
       <c r="F6">
-        <v>42.5</v>
+        <v>41.1</v>
       </c>
       <c r="G6">
-        <v>38.8</v>
+        <v>40.6</v>
       </c>
       <c r="H6">
-        <v>35.7</v>
+        <v>39.9</v>
       </c>
       <c r="I6">
-        <v>33.1</v>
+        <v>39.2</v>
       </c>
       <c r="J6">
-        <v>30.8</v>
+        <v>38.4</v>
       </c>
       <c r="K6">
-        <v>28.7</v>
+        <v>37.6</v>
       </c>
       <c r="L6">
-        <v>26.7</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>86.90000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="C7">
-        <v>85.7</v>
+        <v>60.1</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>58.9</v>
       </c>
       <c r="E7">
-        <v>84.90000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="F7">
-        <v>85.8</v>
+        <v>56.9</v>
       </c>
       <c r="G7">
-        <v>87.8</v>
+        <v>56.2</v>
       </c>
       <c r="H7">
-        <v>90.59999999999999</v>
+        <v>55.9</v>
       </c>
       <c r="I7">
-        <v>93.90000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="J7">
-        <v>97.40000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="K7">
-        <v>100.5</v>
+        <v>56.7</v>
       </c>
       <c r="L7">
-        <v>102.9</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>66</v>
+        <v>43.7</v>
       </c>
       <c r="C8">
-        <v>63.5</v>
+        <v>44.3</v>
       </c>
       <c r="D8">
-        <v>61.4</v>
+        <v>45.3</v>
       </c>
       <c r="E8">
-        <v>60</v>
+        <v>46.3</v>
       </c>
       <c r="F8">
-        <v>59.7</v>
+        <v>47.4</v>
       </c>
       <c r="G8">
-        <v>60.6</v>
+        <v>48.4</v>
       </c>
       <c r="H8">
-        <v>62.6</v>
+        <v>49.2</v>
       </c>
       <c r="I8">
-        <v>65.59999999999999</v>
+        <v>49.9</v>
       </c>
       <c r="J8">
-        <v>69.3</v>
+        <v>50.3</v>
       </c>
       <c r="K8">
-        <v>73.3</v>
+        <v>50.6</v>
       </c>
       <c r="L8">
-        <v>77</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>75.09999999999999</v>
+        <v>53.2</v>
       </c>
       <c r="C9">
-        <v>72.40000000000001</v>
+        <v>53</v>
       </c>
       <c r="D9">
-        <v>69.90000000000001</v>
+        <v>53</v>
       </c>
       <c r="E9">
-        <v>68</v>
+        <v>52.9</v>
       </c>
       <c r="F9">
-        <v>67</v>
+        <v>52.7</v>
       </c>
       <c r="G9">
-        <v>67.09999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="H9">
-        <v>68.2</v>
+        <v>52.5</v>
       </c>
       <c r="I9">
-        <v>70.2</v>
+        <v>52.5</v>
       </c>
       <c r="J9">
-        <v>72.7</v>
+        <v>52.6</v>
       </c>
       <c r="K9">
-        <v>75.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="L9">
-        <v>77.90000000000001</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>82.40000000000001</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>76.8</v>
+        <v>57.5</v>
       </c>
       <c r="D10">
-        <v>71.2</v>
+        <v>56.9</v>
       </c>
       <c r="E10">
-        <v>65.90000000000001</v>
+        <v>56.1</v>
       </c>
       <c r="F10">
-        <v>61.1</v>
+        <v>55.2</v>
       </c>
       <c r="G10">
-        <v>56.8</v>
+        <v>54.2</v>
       </c>
       <c r="H10">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="I10">
-        <v>49.5</v>
+        <v>52.1</v>
       </c>
       <c r="J10">
-        <v>46.2</v>
+        <v>51.1</v>
       </c>
       <c r="K10">
-        <v>42.9</v>
+        <v>50.2</v>
       </c>
       <c r="L10">
-        <v>39.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>99.5</v>
+        <v>81.2</v>
       </c>
       <c r="C11">
-        <v>94.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="D11">
-        <v>90.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="E11">
-        <v>86.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F11">
-        <v>83</v>
+        <v>78.5</v>
       </c>
       <c r="G11">
-        <v>80.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H11">
-        <v>78.2</v>
+        <v>75.5</v>
       </c>
       <c r="I11">
-        <v>76.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="J11">
-        <v>74.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K11">
-        <v>72.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L11">
-        <v>69.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>82.8</v>
+        <v>54</v>
       </c>
       <c r="C12">
-        <v>78.3</v>
+        <v>53.2</v>
       </c>
       <c r="D12">
-        <v>73.59999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="E12">
-        <v>68.8</v>
+        <v>52.1</v>
       </c>
       <c r="F12">
-        <v>64.2</v>
+        <v>51.8</v>
       </c>
       <c r="G12">
-        <v>60</v>
+        <v>51.6</v>
       </c>
       <c r="H12">
-        <v>56.1</v>
+        <v>51.5</v>
       </c>
       <c r="I12">
-        <v>52.5</v>
+        <v>51.4</v>
       </c>
       <c r="J12">
-        <v>49.2</v>
+        <v>51.3</v>
       </c>
       <c r="K12">
-        <v>46.1</v>
+        <v>51.2</v>
       </c>
       <c r="L12">
-        <v>43.2</v>
+        <v>50.9</v>
       </c>
     </row>
   </sheetData>

--- a/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
+++ b/passage_clusters/VIIRS/CLUSTER_2/VCI3M_Forecast_Overview_CLUSTER_2.xlsx
@@ -415,37 +415,37 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="B1" s="1">
-        <v>46260</v>
+        <v>46281</v>
       </c>
       <c r="C1" s="1">
-        <v>46267</v>
+        <v>46288</v>
       </c>
       <c r="D1" s="1">
-        <v>46274</v>
+        <v>46295</v>
       </c>
       <c r="E1" s="1">
-        <v>46281</v>
+        <v>46302</v>
       </c>
       <c r="F1" s="1">
-        <v>46288</v>
+        <v>46309</v>
       </c>
       <c r="G1" s="1">
-        <v>46295</v>
+        <v>46316</v>
       </c>
       <c r="H1" s="1">
-        <v>46302</v>
+        <v>46323</v>
       </c>
       <c r="I1" s="1">
-        <v>46309</v>
+        <v>46330</v>
       </c>
       <c r="J1" s="1">
-        <v>46316</v>
+        <v>46337</v>
       </c>
       <c r="K1" s="1">
-        <v>46323</v>
+        <v>46344</v>
       </c>
       <c r="L1" s="1">
-        <v>46330</v>
+        <v>46351</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -453,37 +453,37 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>54.6</v>
+        <v>52</v>
       </c>
       <c r="C2">
-        <v>53.9</v>
+        <v>51.2</v>
       </c>
       <c r="D2">
-        <v>53.3</v>
+        <v>50.2</v>
       </c>
       <c r="E2">
-        <v>52.6</v>
+        <v>49.4</v>
       </c>
       <c r="F2">
-        <v>52</v>
+        <v>48.6</v>
       </c>
       <c r="G2">
-        <v>51.4</v>
+        <v>48</v>
       </c>
       <c r="H2">
-        <v>50.8</v>
+        <v>47.5</v>
       </c>
       <c r="I2">
-        <v>50.3</v>
+        <v>47.1</v>
       </c>
       <c r="J2">
-        <v>49.8</v>
+        <v>46.7</v>
       </c>
       <c r="K2">
-        <v>49.4</v>
+        <v>46.5</v>
       </c>
       <c r="L2">
-        <v>49.1</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -491,37 +491,37 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="C3">
         <v>48.9</v>
       </c>
       <c r="D3">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
       <c r="E3">
-        <v>48.2</v>
+        <v>49.5</v>
       </c>
       <c r="F3">
-        <v>47.7</v>
+        <v>50</v>
       </c>
       <c r="G3">
-        <v>47</v>
+        <v>50.7</v>
       </c>
       <c r="H3">
-        <v>46.3</v>
+        <v>51.5</v>
       </c>
       <c r="I3">
-        <v>45.5</v>
+        <v>52.3</v>
       </c>
       <c r="J3">
-        <v>44.7</v>
+        <v>53.2</v>
       </c>
       <c r="K3">
-        <v>43.8</v>
+        <v>54.1</v>
       </c>
       <c r="L3">
-        <v>43.1</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -529,37 +529,37 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>58.3</v>
+        <v>52.6</v>
       </c>
       <c r="C4">
-        <v>56.5</v>
+        <v>50.7</v>
       </c>
       <c r="D4">
-        <v>54.8</v>
+        <v>49</v>
       </c>
       <c r="E4">
-        <v>53.2</v>
+        <v>47.5</v>
       </c>
       <c r="F4">
-        <v>51.6</v>
+        <v>46.3</v>
       </c>
       <c r="G4">
-        <v>50.2</v>
+        <v>45.3</v>
       </c>
       <c r="H4">
-        <v>49</v>
+        <v>44.6</v>
       </c>
       <c r="I4">
-        <v>48.1</v>
+        <v>44.1</v>
       </c>
       <c r="J4">
-        <v>47.4</v>
+        <v>43.9</v>
       </c>
       <c r="K4">
-        <v>47</v>
+        <v>43.8</v>
       </c>
       <c r="L4">
-        <v>46.7</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -567,37 +567,37 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>45.5</v>
+        <v>36.7</v>
       </c>
       <c r="C5">
-        <v>42.9</v>
+        <v>33.9</v>
       </c>
       <c r="D5">
-        <v>40.6</v>
+        <v>31.1</v>
       </c>
       <c r="E5">
-        <v>38.6</v>
+        <v>28.6</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>26.2</v>
       </c>
       <c r="G5">
-        <v>35.8</v>
+        <v>24</v>
       </c>
       <c r="H5">
-        <v>34.9</v>
+        <v>22.1</v>
       </c>
       <c r="I5">
-        <v>34.3</v>
+        <v>20.5</v>
       </c>
       <c r="J5">
-        <v>34.1</v>
+        <v>19.2</v>
       </c>
       <c r="K5">
-        <v>34.2</v>
+        <v>18.4</v>
       </c>
       <c r="L5">
-        <v>34.4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -605,37 +605,37 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>41.4</v>
+        <v>41.7</v>
       </c>
       <c r="C6">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="D6">
-        <v>41.6</v>
+        <v>41.8</v>
       </c>
       <c r="E6">
-        <v>41.5</v>
+        <v>42</v>
       </c>
       <c r="F6">
-        <v>41.1</v>
+        <v>42.2</v>
       </c>
       <c r="G6">
-        <v>40.6</v>
+        <v>42.6</v>
       </c>
       <c r="H6">
-        <v>39.9</v>
+        <v>43.1</v>
       </c>
       <c r="I6">
-        <v>39.2</v>
+        <v>43.6</v>
       </c>
       <c r="J6">
-        <v>38.4</v>
+        <v>44.3</v>
       </c>
       <c r="K6">
-        <v>37.6</v>
+        <v>44.9</v>
       </c>
       <c r="L6">
-        <v>36.9</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -643,37 +643,37 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>61.4</v>
+        <v>55.8</v>
       </c>
       <c r="C7">
-        <v>60.1</v>
+        <v>53.8</v>
       </c>
       <c r="D7">
-        <v>58.9</v>
+        <v>51.7</v>
       </c>
       <c r="E7">
-        <v>57.8</v>
+        <v>49.7</v>
       </c>
       <c r="F7">
-        <v>56.9</v>
+        <v>47.9</v>
       </c>
       <c r="G7">
-        <v>56.2</v>
+        <v>46.4</v>
       </c>
       <c r="H7">
-        <v>55.9</v>
+        <v>45.2</v>
       </c>
       <c r="I7">
-        <v>55.9</v>
+        <v>44.2</v>
       </c>
       <c r="J7">
-        <v>56.2</v>
+        <v>43.4</v>
       </c>
       <c r="K7">
-        <v>56.7</v>
+        <v>42.9</v>
       </c>
       <c r="L7">
-        <v>57.4</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -681,37 +681,37 @@
         <v>6</v>
       </c>
       <c r="B8">
+        <v>44.8</v>
+      </c>
+      <c r="C8">
+        <v>45</v>
+      </c>
+      <c r="D8">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>44.8</v>
+      </c>
+      <c r="F8">
+        <v>44.3</v>
+      </c>
+      <c r="G8">
         <v>43.7</v>
       </c>
-      <c r="C8">
-        <v>44.3</v>
-      </c>
-      <c r="D8">
-        <v>45.3</v>
-      </c>
-      <c r="E8">
-        <v>46.3</v>
-      </c>
-      <c r="F8">
-        <v>47.4</v>
-      </c>
-      <c r="G8">
-        <v>48.4</v>
-      </c>
       <c r="H8">
-        <v>49.2</v>
+        <v>43</v>
       </c>
       <c r="I8">
-        <v>49.9</v>
+        <v>42.2</v>
       </c>
       <c r="J8">
-        <v>50.3</v>
+        <v>41.4</v>
       </c>
       <c r="K8">
-        <v>50.6</v>
+        <v>40.8</v>
       </c>
       <c r="L8">
-        <v>50.7</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -719,37 +719,37 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>53.2</v>
+        <v>53.5</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>53.6</v>
       </c>
       <c r="D9">
-        <v>53</v>
+        <v>53.8</v>
       </c>
       <c r="E9">
-        <v>52.9</v>
+        <v>54.1</v>
       </c>
       <c r="F9">
-        <v>52.7</v>
+        <v>54.4</v>
       </c>
       <c r="G9">
-        <v>52.6</v>
+        <v>55</v>
       </c>
       <c r="H9">
-        <v>52.5</v>
+        <v>55.6</v>
       </c>
       <c r="I9">
-        <v>52.5</v>
+        <v>56.4</v>
       </c>
       <c r="J9">
-        <v>52.6</v>
+        <v>57.2</v>
       </c>
       <c r="K9">
-        <v>52.9</v>
+        <v>57.8</v>
       </c>
       <c r="L9">
-        <v>53.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -757,37 +757,37 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>58</v>
+        <v>56.2</v>
       </c>
       <c r="C10">
-        <v>57.5</v>
+        <v>55.4</v>
       </c>
       <c r="D10">
-        <v>56.9</v>
+        <v>54.7</v>
       </c>
       <c r="E10">
-        <v>56.1</v>
+        <v>54</v>
       </c>
       <c r="F10">
-        <v>55.2</v>
+        <v>53.5</v>
       </c>
       <c r="G10">
-        <v>54.2</v>
+        <v>53.1</v>
       </c>
       <c r="H10">
-        <v>53.1</v>
+        <v>52.8</v>
       </c>
       <c r="I10">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="J10">
-        <v>51.1</v>
+        <v>52.6</v>
       </c>
       <c r="K10">
-        <v>50.2</v>
+        <v>52.4</v>
       </c>
       <c r="L10">
-        <v>49.4</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -795,37 +795,37 @@
         <v>9</v>
       </c>
       <c r="B11">
+        <v>80.5</v>
+      </c>
+      <c r="C11">
+        <v>80.3</v>
+      </c>
+      <c r="D11">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="E11">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="F11">
+        <v>80.2</v>
+      </c>
+      <c r="G11">
+        <v>80.5</v>
+      </c>
+      <c r="H11">
+        <v>80.8</v>
+      </c>
+      <c r="I11">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="J11">
         <v>81.2</v>
       </c>
-      <c r="C11">
+      <c r="K11">
         <v>81</v>
       </c>
-      <c r="D11">
-        <v>80.5</v>
-      </c>
-      <c r="E11">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="F11">
-        <v>78.5</v>
-      </c>
-      <c r="G11">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="H11">
-        <v>75.5</v>
-      </c>
-      <c r="I11">
-        <v>73.8</v>
-      </c>
-      <c r="J11">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="K11">
-        <v>69.90000000000001</v>
-      </c>
       <c r="L11">
-        <v>67.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -833,37 +833,37 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>54</v>
+        <v>49.9</v>
       </c>
       <c r="C12">
-        <v>53.2</v>
+        <v>48.2</v>
       </c>
       <c r="D12">
-        <v>52.6</v>
+        <v>46.2</v>
       </c>
       <c r="E12">
-        <v>52.1</v>
+        <v>44</v>
       </c>
       <c r="F12">
-        <v>51.8</v>
+        <v>41.5</v>
       </c>
       <c r="G12">
-        <v>51.6</v>
+        <v>38.9</v>
       </c>
       <c r="H12">
-        <v>51.5</v>
+        <v>36.3</v>
       </c>
       <c r="I12">
-        <v>51.4</v>
+        <v>33.6</v>
       </c>
       <c r="J12">
-        <v>51.3</v>
+        <v>31</v>
       </c>
       <c r="K12">
-        <v>51.2</v>
+        <v>28.7</v>
       </c>
       <c r="L12">
-        <v>50.9</v>
+        <v>26.8</v>
       </c>
     </row>
   </sheetData>
